--- a/artfynd/A 31400-2025 artfynd.xlsx
+++ b/artfynd/A 31400-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137101265</v>
       </c>
       <c r="B2" t="n">
-        <v>98218</v>
+        <v>98224</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31400-2025 artfynd.xlsx
+++ b/artfynd/A 31400-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137101265</v>
       </c>
       <c r="B2" t="n">
-        <v>98224</v>
+        <v>98228</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31400-2025 artfynd.xlsx
+++ b/artfynd/A 31400-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137101265</v>
       </c>
       <c r="B2" t="n">
-        <v>98228</v>
+        <v>98230</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31400-2025 artfynd.xlsx
+++ b/artfynd/A 31400-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137101265</v>
       </c>
       <c r="B2" t="n">
-        <v>98230</v>
+        <v>98232</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31400-2025 artfynd.xlsx
+++ b/artfynd/A 31400-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137101265</v>
       </c>
       <c r="B2" t="n">
-        <v>98232</v>
+        <v>98245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31400-2025 artfynd.xlsx
+++ b/artfynd/A 31400-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137101265</v>
       </c>
       <c r="B2" t="n">
-        <v>98245</v>
+        <v>98247</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31400-2025 artfynd.xlsx
+++ b/artfynd/A 31400-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137101265</v>
       </c>
       <c r="B2" t="n">
-        <v>98247</v>
+        <v>98250</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31400-2025 artfynd.xlsx
+++ b/artfynd/A 31400-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137101265</v>
       </c>
       <c r="B2" t="n">
-        <v>98250</v>
+        <v>98260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31400-2025 artfynd.xlsx
+++ b/artfynd/A 31400-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137101265</v>
       </c>
       <c r="B2" t="n">
-        <v>98260</v>
+        <v>98261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31400-2025 artfynd.xlsx
+++ b/artfynd/A 31400-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137101265</v>
       </c>
       <c r="B2" t="n">
-        <v>98261</v>
+        <v>98266</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31400-2025 artfynd.xlsx
+++ b/artfynd/A 31400-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137101265</v>
       </c>
       <c r="B2" t="n">
-        <v>98266</v>
+        <v>98268</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Carl-Axel Andersson, Magnus J Magnusson</t>
+          <t>Magnus J Magnusson, Carl-Axel Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 31400-2025 artfynd.xlsx
+++ b/artfynd/A 31400-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137101265</v>
       </c>
       <c r="B2" t="n">
-        <v>98268</v>
+        <v>98274</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31400-2025 artfynd.xlsx
+++ b/artfynd/A 31400-2025 artfynd.xlsx
@@ -776,7 +776,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus J Magnusson, Carl-Axel Andersson</t>
+          <t>Carl-Axel Andersson, Magnus J Magnusson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 31400-2025 artfynd.xlsx
+++ b/artfynd/A 31400-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137101265</v>
       </c>
       <c r="B2" t="n">
-        <v>98274</v>
+        <v>98286</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Carl-Axel Andersson, Magnus J Magnusson</t>
+          <t>Magnus J Magnusson, Carl-Axel Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 31400-2025 artfynd.xlsx
+++ b/artfynd/A 31400-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137101265</v>
       </c>
       <c r="B2" t="n">
-        <v>98286</v>
+        <v>98287</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31400-2025 artfynd.xlsx
+++ b/artfynd/A 31400-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137101265</v>
       </c>
       <c r="B2" t="n">
-        <v>98287</v>
+        <v>98290</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31400-2025 artfynd.xlsx
+++ b/artfynd/A 31400-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137101265</v>
       </c>
       <c r="B2" t="n">
-        <v>98290</v>
+        <v>98294</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus J Magnusson, Carl-Axel Andersson</t>
+          <t>Carl-Axel Andersson, Magnus J Magnusson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 31400-2025 artfynd.xlsx
+++ b/artfynd/A 31400-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137101265</v>
       </c>
       <c r="B2" t="n">
-        <v>98294</v>
+        <v>98296</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
